--- a/docs/Decodifiche/11_dec_stato_evento.xlsx
+++ b/docs/Decodifiche/11_dec_stato_evento.xlsx
@@ -92,7 +92,7 @@
     <t>CANCELLATO</t>
   </si>
   <si>
-    <t>2023-12-20 14:57:15.0</t>
+    <t>2023-12-20 16:48:39.0</t>
   </si>
   <si>
     <t>10</t>
@@ -101,7 +101,7 @@
     <t>INEFFICACE</t>
   </si>
   <si>
-    <t>2024-01-23 09:57:09.0</t>
+    <t>2024-01-29 12:09:13.0</t>
   </si>
   <si>
     <t>11</t>
